--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554274393</v>
+        <v>46157.93109751065</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109751065</v>
+        <v>46157.9313410487</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313410487</v>
+        <v>46157.93381637269</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93381637269</v>
+        <v>46157.93693277399</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93693277399</v>
+        <v>46158.2820397453</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820397453</v>
+        <v>46158.29650736609</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29650736609</v>
+        <v>46158.29805441766</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805441766</v>
+        <v>46158.33368576809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33368576809</v>
+        <v>46158.37220467066</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220467066</v>
+        <v>46158.37274551977</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
